--- a/Assets/test260903/chapter0301.xlsx
+++ b/Assets/test260903/chapter0301.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="319" documentId="11_CA461DC239F3CE052E83A027A8BF20349734503B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82161C6D-C387-4D12-B603-CE1008AFF654}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0301" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0301" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="124">
   <si>
     <t>Command</t>
   </si>
@@ -66,9 +75,6 @@
     <t>WaitInput</t>
   </si>
   <si>
-    <t>BgOff</t>
-  </si>
-  <si>
     <t>Chapter3-1です</t>
   </si>
   <si>
@@ -76,27 +82,531 @@
   </si>
   <si>
     <t>*chapter0302_Start</t>
+  </si>
+  <si>
+    <t>Bg</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BGM6</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私、あなたのことが好きです</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>照れ</t>
+  </si>
+  <si>
+    <t>結城奏</t>
+  </si>
+  <si>
+    <t>背景：通学路（3章・夕方）</t>
+  </si>
+  <si>
+    <t>前からずっと、
+ずっと先輩のことが気になっていました</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>どこがどう気になるのかは、
+うまく言葉にできないけれど……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>FadeIn</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>black</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あなたのことを考えると、
+あなたのことしか考えられなくて</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>もっとあなたと一緒にいたいって、
+もっとあなたを知りたいって思うんです</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それで……
+私と、付き合ってほしいんです</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>買い物に行ったり、映画に行ったり、
+本屋さんに行ったり……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>色々なことを、
+あなたとしてみたい……です</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それは、突然の告白だった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>主人公</t>
+  </si>
+  <si>
+    <t>中学三年生になったその日、
+僕はいきなり告白されたのだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>彼女の名前は結城 奏（ゆうき かなで）。
+僕の一つ後輩だ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>告白してもらったのは、正直……嬉しい。
+素直に嬉しい。けれど……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>今のところは、戸惑いの方が大きい</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>結城さんは同じ図書委員だけど、
+そういうキャラじゃないと思っていた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>結城さんは物静かで、
+そういう事には関心がないと思っていた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それに、友達がいないわけじゃないけど、
+1人でいることの方が多いような気がする</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>本人が人を避けているわけではないのに、
+何故か近寄りがたい空気がある</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>結城奏はそういう人間だった。
+だから、この告白は凄く意外だ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>恋人を作ろうと思っていたなんて。
+想像もしなかった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕は中学三年生で卒業を控えているから、
+タイミング的にはイイと思うけど……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……ダメ、ですか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-1-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-1-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ダメじゃないけど……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>結城さんを詳しく知らないから</t>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-1合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そこを何とか、
+えっと……お願いしますっ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>でも……知りたいんです。
+あなたのことを</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……逆に変な感じだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>自慢じゃないけど、僕はモテない。
+なのに、ここまで言われるなんて……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>不安になってくる。
+これは、もしかして……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「僕に告白する」という罰ゲームや、
+何かのイジメなんじゃないだろうか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>でも「罰ゲームですか？」と聞くのは、
+ちょっと悪い。本気だったら、失礼だ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>まずOKしてみよう。
+罰ゲームなら、笑われて終わるだけだし</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-2-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-2-ｂ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>よろしくお願いします！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……ありがとうございます</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それじゃ、今日からカップルですね。
+私たち……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-2合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あはっ……やった♪</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>喜び</t>
+    <rPh sb="0" eb="1">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>よろしくお願いします</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-3-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>はい、こちらこそ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>というわけで、
+僕と結城さんはカップルになった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>とりあえず……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-4-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>もう遅いし、一緒に帰る？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>はい！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>結城さんと一緒に帰ることになった。
+女子と2人きりで行動するなんて初めてだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Se</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>歩く足音</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>うーん、緊張してきた。
+ネタバレはいつになるのだろうか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>しかし結局、ネタバレはなかった。
+その代わり……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：黒</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>StopBgm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……明日から、夏休みですね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：住宅街（夕方）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BGM1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>夏休み……ふふっ、
+私、やりたいことがたくさんあります</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>これまでみたいに、
+付き合ってくれますよね？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>告白されてから三か月、
+僕らは普通にカップルとして過ごした</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>気が付けば結城さんじゃなくて、
+「奏」と下の名前で呼ぶようになった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-5-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-5-ｂ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>罰ゲームじゃなかったんだ……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>喜んで、付き合うよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-5合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>へ？　罰ゲーム？
+なんの話ですか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>な、何でもないよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ありがとうございます</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ワクワクします、私</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>春に告白してから三か月、
+色々なことをしました</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>でも、まだ足りないんです。
+もっと先輩のことを知りたいです</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そのためにも、あなたと一緒にいたい。
+そう思うんです、私……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……凄くうれしい。
+ここまで思ってもらえるなんて</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>でも、分からないことがある。
+どうして僕なんだろう？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>確かに奏といるのは楽しかった。
+話も合うし、趣味も合った</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕も奏が好きだ。
+一緒にいる時間は楽しい。でも……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あれ？
+難しい顔して……どうかしたんですか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-6-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-6-ｂ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>いいや、何でもない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>どうして僕を好きになったのかなって</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ウソです。
+絶対に何か考えていましたよね？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私たち、もう付き合って三か月です。
+隠し事はやめましょう</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……僕のどこが好きなのかなって</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0301-6合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ふふっ、そんなの簡単ですよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>好きになったから、好きになったんです</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>理由なんてありません。
+ただ、あなたのことが好きなんです</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,49 +614,71 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -336,28 +868,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1070"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="39.33203125" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,686 +927,1275 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1"/>
       <c r="H2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30" customHeight="1">
+      <c r="B10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.8" customHeight="1">
+      <c r="B11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" customHeight="1">
+      <c r="B12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="28.2" customHeight="1">
+      <c r="B13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="28.2" customHeight="1">
+      <c r="B14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
+    <row r="15" spans="1:12" ht="30" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="B15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="I15" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
+    <row r="16" spans="1:12" ht="27.6" customHeight="1">
+      <c r="A16" s="1"/>
+      <c r="B16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="13.5" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1">
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="I17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1">
+      <c r="B18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="I18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="28.8" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1">
+      <c r="B19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.8" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" ht="13.5" customHeight="1">
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
+      <c r="B20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A21" s="1"/>
+      <c r="B21" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="B23" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="I23" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="I24" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A26" s="1"/>
+      <c r="B26" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B27" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="I27" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B28" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="I28" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A30" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A31" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" ht="13.5" customHeight="1">
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" ht="13.5" customHeight="1">
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" ht="13.5" customHeight="1">
+    <row r="35" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A35" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" ht="13.5" customHeight="1">
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" ht="13.5" customHeight="1">
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" ht="13.5" customHeight="1">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" ht="13.5" customHeight="1">
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" ht="13.5" customHeight="1">
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" ht="13.5" customHeight="1">
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1">
+    <row r="37" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" customHeight="1">
+      <c r="B38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B39" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="I39" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B40" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="I40" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B41" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B42" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B43" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" customHeight="1">
+      <c r="B44" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A45" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A46" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A47" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="I48" s="1"/>
+    <row r="48" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A48" s="1"/>
+      <c r="B48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="1"/>
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A49" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="C49" s="1"/>
       <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
+    </row>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A50" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="I51" s="1"/>
+    <row r="51" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
+    <row r="52" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A52" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I52" s="1"/>
-    </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A53" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I53" s="1"/>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" ht="13.5" customHeight="1">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A55" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="I55" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="1"/>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" ht="13.5" customHeight="1">
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" ht="13.5" customHeight="1">
+    <row r="57" spans="1:10" ht="30" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B58" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A59" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A60" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" ht="13.5" customHeight="1">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" ht="13.5" customHeight="1">
-      <c r="B62" s="1"/>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A61" s="1"/>
+      <c r="B61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A62" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>82</v>
+      </c>
       <c r="C62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="1"/>
+    <row r="63" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B63" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="C63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" ht="13.5" customHeight="1">
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" ht="13.5" customHeight="1">
-      <c r="B67" s="1"/>
+      <c r="I63" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B64" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="I64" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A65" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="I65" s="6"/>
+    </row>
+    <row r="66" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I66" s="6"/>
+    </row>
+    <row r="67" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A67" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B67" s="9"/>
       <c r="C67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" ht="13.5" customHeight="1">
-      <c r="B70" s="1"/>
+      <c r="I67" s="6"/>
+    </row>
+    <row r="68" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B68" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="I68" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A69" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="I69" s="6"/>
+    </row>
+    <row r="70" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A70" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="C70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" ht="13.5" customHeight="1">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" ht="13.5" customHeight="1">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" ht="13.5" customHeight="1">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" ht="13.5" customHeight="1">
-      <c r="B74" s="1"/>
+      <c r="I70" s="6"/>
+    </row>
+    <row r="71" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B71" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="30" customHeight="1">
+      <c r="A72" s="1"/>
+      <c r="B72" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="27" customHeight="1">
+      <c r="A73" s="1"/>
+      <c r="B73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H73" s="1"/>
+      <c r="I73" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="30" customHeight="1">
+      <c r="B74" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="C74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" ht="13.5" customHeight="1">
-      <c r="B75" s="1"/>
+      <c r="I74" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="30" customHeight="1">
+      <c r="B75" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="C75" s="1"/>
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" ht="13.5" customHeight="1">
+      <c r="I75" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A76" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A77" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H77" s="1"/>
+      <c r="I77" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A78" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" ht="13.5" customHeight="1">
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1">
+    </row>
+    <row r="79" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A79" s="1"/>
+      <c r="B79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="14.4" customHeight="1">
+      <c r="A80" s="1"/>
+      <c r="B80" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="I80" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A81" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81" s="1"/>
       <c r="I81" s="1"/>
     </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1">
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1">
+      <c r="B83" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
       <c r="A84" s="1"/>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
-      <c r="B85" s="1"/>
+      <c r="B84" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A85" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="C85" s="1"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" ht="13.5" customHeight="1">
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A86" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="I86" s="1"/>
     </row>
-    <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" ht="13.5" customHeight="1">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" ht="13.5" customHeight="1">
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" ht="13.5" customHeight="1">
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="I93" s="1"/>
-    </row>
-    <row r="94" ht="13.5" customHeight="1">
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="I94" s="1"/>
-    </row>
-    <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-    </row>
-    <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" ht="13.5" customHeight="1">
+    <row r="87" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B87" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B88" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B89" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B90" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" s="1"/>
+      <c r="I90" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B91" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B92" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B93" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A94" s="1"/>
+      <c r="B94" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A95" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J95" s="1"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A96" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A97" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" ht="13.5" customHeight="1">
-      <c r="I98" s="1"/>
-    </row>
-    <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-      <c r="I99" s="1"/>
-    </row>
-    <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-    </row>
-    <row r="101" ht="13.5" customHeight="1">
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" ht="13.5" customHeight="1">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" ht="13.5" customHeight="1">
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" ht="13.5" customHeight="1">
+    <row r="98" spans="1:9" ht="30" customHeight="1">
+      <c r="B98" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B99" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B100" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C100" s="1"/>
+      <c r="I100" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A101" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A102" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B103" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A104" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C104" s="1"/>
       <c r="I104" s="1"/>
     </row>
-    <row r="105" ht="13.5" customHeight="1">
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A105" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
-      <c r="I106" s="1"/>
-    </row>
-    <row r="107" ht="13.5" customHeight="1">
-      <c r="I107" s="1"/>
-    </row>
-    <row r="108" ht="13.5" customHeight="1">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="I108" s="1"/>
-    </row>
-    <row r="109" ht="13.5" customHeight="1">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B106" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A107" s="1"/>
+      <c r="B107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I107" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
       <c r="I109" s="1"/>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
       <c r="I110" s="1"/>
     </row>
-    <row r="111" ht="13.5" customHeight="1">
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A111" s="1"/>
       <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
+    <row r="112" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A112" s="1"/>
+      <c r="H112" s="1"/>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" s="1"/>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
       <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" ht="13.5" customHeight="1">
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="I116" s="1"/>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1">
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
       <c r="I119" s="1"/>
     </row>
-    <row r="120" ht="13.5" customHeight="1">
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" ht="13.5" customHeight="1">
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="1"/>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="B122" s="1"/>
-    </row>
-    <row r="123" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
       <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" ht="13.5" customHeight="1">
+    </row>
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="I124" s="1"/>
     </row>
-    <row r="125" ht="13.5" customHeight="1">
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A125" s="1"/>
       <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
       <c r="I125" s="1"/>
-    </row>
-    <row r="126" ht="13.5" customHeight="1">
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
-    </row>
-    <row r="127" ht="13.5" customHeight="1">
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+    </row>
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
-    </row>
-    <row r="128" ht="13.5" customHeight="1">
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
       <c r="I128" s="1"/>
     </row>
-    <row r="129" ht="13.5" customHeight="1">
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
       <c r="A129" s="1"/>
-    </row>
-    <row r="130" ht="13.5" customHeight="1">
+      <c r="B129" s="1"/>
+    </row>
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
       <c r="A130" s="1"/>
     </row>
-    <row r="131" ht="13.5" customHeight="1">
-      <c r="A131" s="1"/>
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
       <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
+      <c r="C131" s="1"/>
       <c r="I131" s="1"/>
     </row>
-    <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
+    <row r="132" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" ht="13.5" customHeight="1">
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
       <c r="I133" s="1"/>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
-      <c r="I134" s="1"/>
-    </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
       <c r="I135" s="1"/>
-    </row>
-    <row r="136" ht="13.5" customHeight="1">
+      <c r="J135" s="1"/>
+    </row>
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
       <c r="I136" s="1"/>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
       <c r="I137" s="1"/>
     </row>
-    <row r="138" ht="13.5" customHeight="1">
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" ht="13.5" customHeight="1">
-      <c r="I139" s="1"/>
-    </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
-    <row r="145" ht="13.5" customHeight="1"/>
-    <row r="146" ht="13.5" customHeight="1"/>
-    <row r="147" ht="13.5" customHeight="1"/>
-    <row r="148" ht="13.5" customHeight="1"/>
-    <row r="149" ht="13.5" customHeight="1"/>
-    <row r="150" ht="13.5" customHeight="1"/>
-    <row r="151" ht="13.5" customHeight="1"/>
-    <row r="152" ht="13.5" customHeight="1"/>
-    <row r="153" ht="13.5" customHeight="1"/>
-    <row r="154" ht="13.5" customHeight="1"/>
-    <row r="155" ht="13.5" customHeight="1"/>
-    <row r="156" ht="13.5" customHeight="1"/>
-    <row r="157" ht="13.5" customHeight="1"/>
-    <row r="158" ht="13.5" customHeight="1"/>
-    <row r="159" ht="13.5" customHeight="1"/>
-    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+    </row>
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="1"/>
+    </row>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A141" s="1"/>
+    </row>
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A142" s="1"/>
+    </row>
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I148" s="1"/>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I149" s="1"/>
+    </row>
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I150" s="1"/>
+    </row>
+    <row r="151" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I151" s="1"/>
+    </row>
+    <row r="152" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="153" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="154" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="155" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="156" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="157" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="158" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A158" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="160" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="161" ht="13.5" customHeight="1"/>
     <row r="162" ht="13.5" customHeight="1"/>
     <row r="163" ht="13.5" customHeight="1"/>
@@ -1973,10 +3094,21 @@
     <row r="1056" ht="13.5" customHeight="1"/>
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
+    <row r="1059" ht="13.5" customHeight="1"/>
+    <row r="1060" ht="13.5" customHeight="1"/>
+    <row r="1061" ht="13.5" customHeight="1"/>
+    <row r="1062" ht="13.5" customHeight="1"/>
+    <row r="1063" ht="13.5" customHeight="1"/>
+    <row r="1064" ht="13.5" customHeight="1"/>
+    <row r="1065" ht="13.5" customHeight="1"/>
+    <row r="1066" ht="13.5" customHeight="1"/>
+    <row r="1067" ht="13.5" customHeight="1"/>
+    <row r="1068" ht="13.5" customHeight="1"/>
+    <row r="1069" ht="13.5" customHeight="1"/>
+    <row r="1070" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>